--- a/Hand_edited_log/1/student/AnhDThe187386/OverallSummary.xlsx
+++ b/Hand_edited_log/1/student/AnhDThe187386/OverallSummary.xlsx
@@ -37,7 +37,7 @@
     <x:t>FAIL</x:t>
   </x:si>
   <x:si>
-    <x:t>Network monitoring failed: No packets captured. Run with sudo and ensure libpcap/NPcap is installed.</x:t>
+    <x:t/>
   </x:si>
   <x:si>
     <x:t>TC2</x:t>
@@ -425,7 +425,7 @@
     <x:col min="2" max="2" width="7.282054" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="92.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="5.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" s="1" customFormat="1">

--- a/Hand_edited_log/1/student/AnhDThe187386/OverallSummary.xlsx
+++ b/Hand_edited_log/1/student/AnhDThe187386/OverallSummary.xlsx
@@ -34,7 +34,7 @@
     <x:t>TC1</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
+    <x:t>PASS</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -453,10 +453,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
         <x:v>7</x:v>
@@ -470,10 +470,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>7</x:v>
@@ -487,10 +487,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>7</x:v>
@@ -504,10 +504,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>7</x:v>
@@ -521,10 +521,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>7</x:v>
@@ -538,10 +538,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>7</x:v>
